--- a/Strivers_A2Z_DSA_Sheet.xlsx
+++ b/Strivers_A2Z_DSA_Sheet.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Striver&amp;apos;s A2Z DSA Sheet"/>
+    <sheet r:id="rId1" sheetId="1" name="Striver&amp;amp;apos;s A2Z DSA Sheet"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="179">
   <si>
     <t>📚 Striver&amp;apos;s A2Z DSA Course - Progress Tracker</t>
   </si>
@@ -582,7 +582,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -626,12 +626,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FFcccccc"/>
       <name val="Calibri"/>
@@ -640,6 +634,12 @@
     <font>
       <sz val="14"/>
       <color rgb="FF00c853"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -689,7 +689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -742,6 +742,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -793,40 +800,40 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="12" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="13" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
@@ -1262,7 +1269,9 @@
       <c r="C8" s="15">
         <v>1</v>
       </c>
-      <c r="D8" s="24"/>
+      <c r="D8" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="17" t="s">
         <v>14</v>
       </c>
@@ -1278,7 +1287,7 @@
       <c r="C9" s="21">
         <v>7</v>
       </c>
-      <c r="D9" s="25"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="22" t="s">
         <v>14</v>
       </c>
@@ -1294,7 +1303,7 @@
       <c r="C10" s="15">
         <v>9</v>
       </c>
-      <c r="D10" s="24"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="17" t="s">
         <v>14</v>
       </c>
@@ -1310,13 +1319,13 @@
       <c r="C11" s="21">
         <v>6</v>
       </c>
-      <c r="D11" s="25"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="23"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -1348,7 +1357,7 @@
       <c r="C14" s="15">
         <v>3</v>
       </c>
-      <c r="D14" s="24"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="17" t="s">
         <v>14</v>
       </c>
@@ -1364,13 +1373,13 @@
       <c r="C15" s="21">
         <v>4</v>
       </c>
-      <c r="D15" s="25"/>
+      <c r="D15" s="24"/>
       <c r="E15" s="22" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="23"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -1402,7 +1411,7 @@
       <c r="C18" s="15">
         <v>14</v>
       </c>
-      <c r="D18" s="24"/>
+      <c r="D18" s="25"/>
       <c r="E18" s="17" t="s">
         <v>14</v>
       </c>
@@ -1418,7 +1427,7 @@
       <c r="C19" s="21">
         <v>14</v>
       </c>
-      <c r="D19" s="25"/>
+      <c r="D19" s="24"/>
       <c r="E19" s="22" t="s">
         <v>14</v>
       </c>
@@ -1434,13 +1443,13 @@
       <c r="C20" s="15">
         <v>12</v>
       </c>
-      <c r="D20" s="24"/>
+      <c r="D20" s="25"/>
       <c r="E20" s="17" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="18"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
@@ -1472,7 +1481,7 @@
       <c r="C23" s="15">
         <v>13</v>
       </c>
-      <c r="D23" s="24"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="17" t="s">
         <v>14</v>
       </c>
@@ -1488,7 +1497,7 @@
       <c r="C24" s="21">
         <v>11</v>
       </c>
-      <c r="D24" s="25"/>
+      <c r="D24" s="24"/>
       <c r="E24" s="22" t="s">
         <v>14</v>
       </c>
@@ -1504,13 +1513,13 @@
       <c r="C25" s="15">
         <v>8</v>
       </c>
-      <c r="D25" s="24"/>
+      <c r="D25" s="25"/>
       <c r="E25" s="17" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="18"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="6"/>
@@ -1542,7 +1551,7 @@
       <c r="C28" s="15">
         <v>7</v>
       </c>
-      <c r="D28" s="24"/>
+      <c r="D28" s="25"/>
       <c r="E28" s="17" t="s">
         <v>14</v>
       </c>
@@ -1558,7 +1567,7 @@
       <c r="C29" s="21">
         <v>8</v>
       </c>
-      <c r="D29" s="25"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="22" t="s">
         <v>14</v>
       </c>
@@ -1596,7 +1605,7 @@
       <c r="C32" s="15">
         <v>6</v>
       </c>
-      <c r="D32" s="24"/>
+      <c r="D32" s="25"/>
       <c r="E32" s="17" t="s">
         <v>14</v>
       </c>
@@ -1612,7 +1621,7 @@
       <c r="C33" s="21">
         <v>4</v>
       </c>
-      <c r="D33" s="25"/>
+      <c r="D33" s="24"/>
       <c r="E33" s="22" t="s">
         <v>14</v>
       </c>
@@ -1628,7 +1637,7 @@
       <c r="C34" s="15">
         <v>15</v>
       </c>
-      <c r="D34" s="24"/>
+      <c r="D34" s="25"/>
       <c r="E34" s="17" t="s">
         <v>14</v>
       </c>
@@ -1644,7 +1653,7 @@
       <c r="C35" s="21">
         <v>1</v>
       </c>
-      <c r="D35" s="25"/>
+      <c r="D35" s="24"/>
       <c r="E35" s="22" t="s">
         <v>14</v>
       </c>
@@ -1660,7 +1669,7 @@
       <c r="C36" s="15">
         <v>5</v>
       </c>
-      <c r="D36" s="24"/>
+      <c r="D36" s="25"/>
       <c r="E36" s="17" t="s">
         <v>14</v>
       </c>
@@ -1698,7 +1707,7 @@
       <c r="C39" s="15">
         <v>5</v>
       </c>
-      <c r="D39" s="24"/>
+      <c r="D39" s="25"/>
       <c r="E39" s="17" t="s">
         <v>14</v>
       </c>
@@ -1714,7 +1723,7 @@
       <c r="C40" s="21">
         <v>14</v>
       </c>
-      <c r="D40" s="25"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="22" t="s">
         <v>14</v>
       </c>
@@ -1730,7 +1739,7 @@
       <c r="C41" s="15">
         <v>6</v>
       </c>
-      <c r="D41" s="24"/>
+      <c r="D41" s="25"/>
       <c r="E41" s="17" t="s">
         <v>14</v>
       </c>
@@ -1768,7 +1777,7 @@
       <c r="C44" s="15">
         <v>8</v>
       </c>
-      <c r="D44" s="24"/>
+      <c r="D44" s="25"/>
       <c r="E44" s="17" t="s">
         <v>14</v>
       </c>
@@ -1784,7 +1793,7 @@
       <c r="C45" s="21">
         <v>5</v>
       </c>
-      <c r="D45" s="25"/>
+      <c r="D45" s="24"/>
       <c r="E45" s="22" t="s">
         <v>14</v>
       </c>
@@ -1800,7 +1809,7 @@
       <c r="C46" s="15">
         <v>5</v>
       </c>
-      <c r="D46" s="24"/>
+      <c r="D46" s="25"/>
       <c r="E46" s="17" t="s">
         <v>14</v>
       </c>
@@ -1838,7 +1847,7 @@
       <c r="C49" s="15">
         <v>8</v>
       </c>
-      <c r="D49" s="24"/>
+      <c r="D49" s="25"/>
       <c r="E49" s="17" t="s">
         <v>14</v>
       </c>
@@ -1854,7 +1863,7 @@
       <c r="C50" s="21">
         <v>6</v>
       </c>
-      <c r="D50" s="25"/>
+      <c r="D50" s="24"/>
       <c r="E50" s="22" t="s">
         <v>14</v>
       </c>
@@ -1870,7 +1879,7 @@
       <c r="C51" s="15">
         <v>10</v>
       </c>
-      <c r="D51" s="24"/>
+      <c r="D51" s="25"/>
       <c r="E51" s="17" t="s">
         <v>14</v>
       </c>
@@ -1886,7 +1895,7 @@
       <c r="C52" s="21">
         <v>6</v>
       </c>
-      <c r="D52" s="25"/>
+      <c r="D52" s="24"/>
       <c r="E52" s="22" t="s">
         <v>14</v>
       </c>
@@ -1924,7 +1933,7 @@
       <c r="C55" s="15">
         <v>6</v>
       </c>
-      <c r="D55" s="24"/>
+      <c r="D55" s="25"/>
       <c r="E55" s="17" t="s">
         <v>14</v>
       </c>
@@ -1940,7 +1949,7 @@
       <c r="C56" s="21">
         <v>6</v>
       </c>
-      <c r="D56" s="25"/>
+      <c r="D56" s="24"/>
       <c r="E56" s="22" t="s">
         <v>14</v>
       </c>
@@ -1978,7 +1987,7 @@
       <c r="C59" s="15">
         <v>3</v>
       </c>
-      <c r="D59" s="24"/>
+      <c r="D59" s="25"/>
       <c r="E59" s="17" t="s">
         <v>14</v>
       </c>
@@ -1994,7 +2003,7 @@
       <c r="C60" s="21">
         <v>8</v>
       </c>
-      <c r="D60" s="25"/>
+      <c r="D60" s="24"/>
       <c r="E60" s="22" t="s">
         <v>14</v>
       </c>
@@ -2010,7 +2019,7 @@
       <c r="C61" s="15">
         <v>6</v>
       </c>
-      <c r="D61" s="24"/>
+      <c r="D61" s="25"/>
       <c r="E61" s="17" t="s">
         <v>14</v>
       </c>
@@ -2048,7 +2057,7 @@
       <c r="C64" s="15">
         <v>6</v>
       </c>
-      <c r="D64" s="24"/>
+      <c r="D64" s="25"/>
       <c r="E64" s="17" t="s">
         <v>14</v>
       </c>
@@ -2064,7 +2073,7 @@
       <c r="C65" s="21">
         <v>10</v>
       </c>
-      <c r="D65" s="25"/>
+      <c r="D65" s="24"/>
       <c r="E65" s="22" t="s">
         <v>14</v>
       </c>
@@ -2102,7 +2111,7 @@
       <c r="C68" s="15">
         <v>13</v>
       </c>
-      <c r="D68" s="24"/>
+      <c r="D68" s="25"/>
       <c r="E68" s="17" t="s">
         <v>14</v>
       </c>
@@ -2118,7 +2127,7 @@
       <c r="C69" s="21">
         <v>12</v>
       </c>
-      <c r="D69" s="25"/>
+      <c r="D69" s="24"/>
       <c r="E69" s="22" t="s">
         <v>14</v>
       </c>
@@ -2134,7 +2143,7 @@
       <c r="C70" s="15">
         <v>14</v>
       </c>
-      <c r="D70" s="24"/>
+      <c r="D70" s="25"/>
       <c r="E70" s="17" t="s">
         <v>14</v>
       </c>
@@ -2172,7 +2181,7 @@
       <c r="C73" s="15">
         <v>4</v>
       </c>
-      <c r="D73" s="24"/>
+      <c r="D73" s="25"/>
       <c r="E73" s="17" t="s">
         <v>14</v>
       </c>
@@ -2188,7 +2197,7 @@
       <c r="C74" s="21">
         <v>12</v>
       </c>
-      <c r="D74" s="25"/>
+      <c r="D74" s="24"/>
       <c r="E74" s="22" t="s">
         <v>14</v>
       </c>
@@ -2226,7 +2235,7 @@
       <c r="C77" s="15">
         <v>6</v>
       </c>
-      <c r="D77" s="24"/>
+      <c r="D77" s="25"/>
       <c r="E77" s="17" t="s">
         <v>14</v>
       </c>
@@ -2242,7 +2251,7 @@
       <c r="C78" s="21">
         <v>14</v>
       </c>
-      <c r="D78" s="25"/>
+      <c r="D78" s="24"/>
       <c r="E78" s="22" t="s">
         <v>14</v>
       </c>
@@ -2258,7 +2267,7 @@
       <c r="C79" s="15">
         <v>7</v>
       </c>
-      <c r="D79" s="24"/>
+      <c r="D79" s="25"/>
       <c r="E79" s="17" t="s">
         <v>14</v>
       </c>
@@ -2274,7 +2283,7 @@
       <c r="C80" s="21">
         <v>12</v>
       </c>
-      <c r="D80" s="25"/>
+      <c r="D80" s="24"/>
       <c r="E80" s="22" t="s">
         <v>14</v>
       </c>
@@ -2290,7 +2299,7 @@
       <c r="C81" s="15">
         <v>8</v>
       </c>
-      <c r="D81" s="24"/>
+      <c r="D81" s="25"/>
       <c r="E81" s="17" t="s">
         <v>14</v>
       </c>
@@ -2306,7 +2315,7 @@
       <c r="C82" s="21">
         <v>6</v>
       </c>
-      <c r="D82" s="25"/>
+      <c r="D82" s="24"/>
       <c r="E82" s="22" t="s">
         <v>14</v>
       </c>
@@ -2344,7 +2353,7 @@
       <c r="C85" s="15">
         <v>1</v>
       </c>
-      <c r="D85" s="24"/>
+      <c r="D85" s="25"/>
       <c r="E85" s="17" t="s">
         <v>14</v>
       </c>
@@ -2360,7 +2369,7 @@
       <c r="C86" s="21">
         <v>5</v>
       </c>
-      <c r="D86" s="25"/>
+      <c r="D86" s="24"/>
       <c r="E86" s="22" t="s">
         <v>14</v>
       </c>
@@ -2376,7 +2385,7 @@
       <c r="C87" s="15">
         <v>7</v>
       </c>
-      <c r="D87" s="24"/>
+      <c r="D87" s="25"/>
       <c r="E87" s="17" t="s">
         <v>14</v>
       </c>
@@ -2392,7 +2401,7 @@
       <c r="C88" s="21">
         <v>9</v>
       </c>
-      <c r="D88" s="25"/>
+      <c r="D88" s="24"/>
       <c r="E88" s="22" t="s">
         <v>14</v>
       </c>
@@ -2408,7 +2417,7 @@
       <c r="C89" s="15">
         <v>10</v>
       </c>
-      <c r="D89" s="24"/>
+      <c r="D89" s="25"/>
       <c r="E89" s="17" t="s">
         <v>14</v>
       </c>
@@ -2424,7 +2433,7 @@
       <c r="C90" s="21">
         <v>6</v>
       </c>
-      <c r="D90" s="25"/>
+      <c r="D90" s="24"/>
       <c r="E90" s="22" t="s">
         <v>14</v>
       </c>
@@ -2440,7 +2449,7 @@
       <c r="C91" s="15">
         <v>5</v>
       </c>
-      <c r="D91" s="24"/>
+      <c r="D91" s="25"/>
       <c r="E91" s="17" t="s">
         <v>14</v>
       </c>
@@ -2456,7 +2465,7 @@
       <c r="C92" s="21">
         <v>7</v>
       </c>
-      <c r="D92" s="25"/>
+      <c r="D92" s="24"/>
       <c r="E92" s="22" t="s">
         <v>14</v>
       </c>
@@ -2472,7 +2481,7 @@
       <c r="C93" s="15">
         <v>1</v>
       </c>
-      <c r="D93" s="24"/>
+      <c r="D93" s="25"/>
       <c r="E93" s="17" t="s">
         <v>14</v>
       </c>
@@ -2488,7 +2497,7 @@
       <c r="C94" s="21">
         <v>5</v>
       </c>
-      <c r="D94" s="25"/>
+      <c r="D94" s="24"/>
       <c r="E94" s="22" t="s">
         <v>14</v>
       </c>
@@ -2526,7 +2535,7 @@
       <c r="C97" s="15">
         <v>1</v>
       </c>
-      <c r="D97" s="24"/>
+      <c r="D97" s="25"/>
       <c r="E97" s="17" t="s">
         <v>14</v>
       </c>
@@ -2542,7 +2551,7 @@
       <c r="C98" s="21">
         <v>6</v>
       </c>
-      <c r="D98" s="25"/>
+      <c r="D98" s="24"/>
       <c r="E98" s="22" t="s">
         <v>14</v>
       </c>
@@ -2580,7 +2589,7 @@
       <c r="C101" s="15">
         <v>9</v>
       </c>
-      <c r="D101" s="24"/>
+      <c r="D101" s="25"/>
       <c r="E101" s="17" t="s">
         <v>14</v>
       </c>

--- a/Strivers_A2Z_DSA_Sheet.xlsx
+++ b/Strivers_A2Z_DSA_Sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="179">
   <si>
     <t>📚 Striver&amp;apos;s A2Z DSA Course - Progress Tracker</t>
   </si>
@@ -824,10 +824,10 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="11" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="12" applyFont="1" fillId="0" applyAlignment="1">
@@ -1287,7 +1287,9 @@
       <c r="C9" s="21">
         <v>7</v>
       </c>
-      <c r="D9" s="24"/>
+      <c r="D9" s="16" t="s">
+        <v>13</v>
+      </c>
       <c r="E9" s="22" t="s">
         <v>14</v>
       </c>
@@ -1303,7 +1305,7 @@
       <c r="C10" s="15">
         <v>9</v>
       </c>
-      <c r="D10" s="25"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="17" t="s">
         <v>14</v>
       </c>
@@ -1319,7 +1321,7 @@
       <c r="C11" s="21">
         <v>6</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="22" t="s">
         <v>14</v>
       </c>
@@ -1357,7 +1359,7 @@
       <c r="C14" s="15">
         <v>3</v>
       </c>
-      <c r="D14" s="25"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="17" t="s">
         <v>14</v>
       </c>
@@ -1373,7 +1375,7 @@
       <c r="C15" s="21">
         <v>4</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="22" t="s">
         <v>14</v>
       </c>
@@ -1411,7 +1413,7 @@
       <c r="C18" s="15">
         <v>14</v>
       </c>
-      <c r="D18" s="25"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="17" t="s">
         <v>14</v>
       </c>
@@ -1427,7 +1429,7 @@
       <c r="C19" s="21">
         <v>14</v>
       </c>
-      <c r="D19" s="24"/>
+      <c r="D19" s="25"/>
       <c r="E19" s="22" t="s">
         <v>14</v>
       </c>
@@ -1443,7 +1445,7 @@
       <c r="C20" s="15">
         <v>12</v>
       </c>
-      <c r="D20" s="25"/>
+      <c r="D20" s="24"/>
       <c r="E20" s="17" t="s">
         <v>14</v>
       </c>
@@ -1481,7 +1483,7 @@
       <c r="C23" s="15">
         <v>13</v>
       </c>
-      <c r="D23" s="25"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="17" t="s">
         <v>14</v>
       </c>
@@ -1497,7 +1499,7 @@
       <c r="C24" s="21">
         <v>11</v>
       </c>
-      <c r="D24" s="24"/>
+      <c r="D24" s="25"/>
       <c r="E24" s="22" t="s">
         <v>14</v>
       </c>
@@ -1513,7 +1515,7 @@
       <c r="C25" s="15">
         <v>8</v>
       </c>
-      <c r="D25" s="25"/>
+      <c r="D25" s="24"/>
       <c r="E25" s="17" t="s">
         <v>14</v>
       </c>
@@ -1551,7 +1553,7 @@
       <c r="C28" s="15">
         <v>7</v>
       </c>
-      <c r="D28" s="25"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="17" t="s">
         <v>14</v>
       </c>
@@ -1567,7 +1569,7 @@
       <c r="C29" s="21">
         <v>8</v>
       </c>
-      <c r="D29" s="24"/>
+      <c r="D29" s="25"/>
       <c r="E29" s="22" t="s">
         <v>14</v>
       </c>
@@ -1605,7 +1607,7 @@
       <c r="C32" s="15">
         <v>6</v>
       </c>
-      <c r="D32" s="25"/>
+      <c r="D32" s="24"/>
       <c r="E32" s="17" t="s">
         <v>14</v>
       </c>
@@ -1621,7 +1623,7 @@
       <c r="C33" s="21">
         <v>4</v>
       </c>
-      <c r="D33" s="24"/>
+      <c r="D33" s="25"/>
       <c r="E33" s="22" t="s">
         <v>14</v>
       </c>
@@ -1637,7 +1639,7 @@
       <c r="C34" s="15">
         <v>15</v>
       </c>
-      <c r="D34" s="25"/>
+      <c r="D34" s="24"/>
       <c r="E34" s="17" t="s">
         <v>14</v>
       </c>
@@ -1653,7 +1655,7 @@
       <c r="C35" s="21">
         <v>1</v>
       </c>
-      <c r="D35" s="24"/>
+      <c r="D35" s="25"/>
       <c r="E35" s="22" t="s">
         <v>14</v>
       </c>
@@ -1669,7 +1671,7 @@
       <c r="C36" s="15">
         <v>5</v>
       </c>
-      <c r="D36" s="25"/>
+      <c r="D36" s="24"/>
       <c r="E36" s="17" t="s">
         <v>14</v>
       </c>
@@ -1707,7 +1709,7 @@
       <c r="C39" s="15">
         <v>5</v>
       </c>
-      <c r="D39" s="25"/>
+      <c r="D39" s="24"/>
       <c r="E39" s="17" t="s">
         <v>14</v>
       </c>
@@ -1723,7 +1725,7 @@
       <c r="C40" s="21">
         <v>14</v>
       </c>
-      <c r="D40" s="24"/>
+      <c r="D40" s="25"/>
       <c r="E40" s="22" t="s">
         <v>14</v>
       </c>
@@ -1739,7 +1741,7 @@
       <c r="C41" s="15">
         <v>6</v>
       </c>
-      <c r="D41" s="25"/>
+      <c r="D41" s="24"/>
       <c r="E41" s="17" t="s">
         <v>14</v>
       </c>
@@ -1777,7 +1779,7 @@
       <c r="C44" s="15">
         <v>8</v>
       </c>
-      <c r="D44" s="25"/>
+      <c r="D44" s="24"/>
       <c r="E44" s="17" t="s">
         <v>14</v>
       </c>
@@ -1793,7 +1795,7 @@
       <c r="C45" s="21">
         <v>5</v>
       </c>
-      <c r="D45" s="24"/>
+      <c r="D45" s="25"/>
       <c r="E45" s="22" t="s">
         <v>14</v>
       </c>
@@ -1809,7 +1811,7 @@
       <c r="C46" s="15">
         <v>5</v>
       </c>
-      <c r="D46" s="25"/>
+      <c r="D46" s="24"/>
       <c r="E46" s="17" t="s">
         <v>14</v>
       </c>
@@ -1847,7 +1849,7 @@
       <c r="C49" s="15">
         <v>8</v>
       </c>
-      <c r="D49" s="25"/>
+      <c r="D49" s="24"/>
       <c r="E49" s="17" t="s">
         <v>14</v>
       </c>
@@ -1863,7 +1865,7 @@
       <c r="C50" s="21">
         <v>6</v>
       </c>
-      <c r="D50" s="24"/>
+      <c r="D50" s="25"/>
       <c r="E50" s="22" t="s">
         <v>14</v>
       </c>
@@ -1879,7 +1881,7 @@
       <c r="C51" s="15">
         <v>10</v>
       </c>
-      <c r="D51" s="25"/>
+      <c r="D51" s="24"/>
       <c r="E51" s="17" t="s">
         <v>14</v>
       </c>
@@ -1895,7 +1897,7 @@
       <c r="C52" s="21">
         <v>6</v>
       </c>
-      <c r="D52" s="24"/>
+      <c r="D52" s="25"/>
       <c r="E52" s="22" t="s">
         <v>14</v>
       </c>
@@ -1933,7 +1935,7 @@
       <c r="C55" s="15">
         <v>6</v>
       </c>
-      <c r="D55" s="25"/>
+      <c r="D55" s="24"/>
       <c r="E55" s="17" t="s">
         <v>14</v>
       </c>
@@ -1949,7 +1951,7 @@
       <c r="C56" s="21">
         <v>6</v>
       </c>
-      <c r="D56" s="24"/>
+      <c r="D56" s="25"/>
       <c r="E56" s="22" t="s">
         <v>14</v>
       </c>
@@ -1987,7 +1989,7 @@
       <c r="C59" s="15">
         <v>3</v>
       </c>
-      <c r="D59" s="25"/>
+      <c r="D59" s="24"/>
       <c r="E59" s="17" t="s">
         <v>14</v>
       </c>
@@ -2003,7 +2005,7 @@
       <c r="C60" s="21">
         <v>8</v>
       </c>
-      <c r="D60" s="24"/>
+      <c r="D60" s="25"/>
       <c r="E60" s="22" t="s">
         <v>14</v>
       </c>
@@ -2019,7 +2021,7 @@
       <c r="C61" s="15">
         <v>6</v>
       </c>
-      <c r="D61" s="25"/>
+      <c r="D61" s="24"/>
       <c r="E61" s="17" t="s">
         <v>14</v>
       </c>
@@ -2057,7 +2059,7 @@
       <c r="C64" s="15">
         <v>6</v>
       </c>
-      <c r="D64" s="25"/>
+      <c r="D64" s="24"/>
       <c r="E64" s="17" t="s">
         <v>14</v>
       </c>
@@ -2073,7 +2075,7 @@
       <c r="C65" s="21">
         <v>10</v>
       </c>
-      <c r="D65" s="24"/>
+      <c r="D65" s="25"/>
       <c r="E65" s="22" t="s">
         <v>14</v>
       </c>
@@ -2111,7 +2113,7 @@
       <c r="C68" s="15">
         <v>13</v>
       </c>
-      <c r="D68" s="25"/>
+      <c r="D68" s="24"/>
       <c r="E68" s="17" t="s">
         <v>14</v>
       </c>
@@ -2127,7 +2129,7 @@
       <c r="C69" s="21">
         <v>12</v>
       </c>
-      <c r="D69" s="24"/>
+      <c r="D69" s="25"/>
       <c r="E69" s="22" t="s">
         <v>14</v>
       </c>
@@ -2143,7 +2145,7 @@
       <c r="C70" s="15">
         <v>14</v>
       </c>
-      <c r="D70" s="25"/>
+      <c r="D70" s="24"/>
       <c r="E70" s="17" t="s">
         <v>14</v>
       </c>
@@ -2181,7 +2183,7 @@
       <c r="C73" s="15">
         <v>4</v>
       </c>
-      <c r="D73" s="25"/>
+      <c r="D73" s="24"/>
       <c r="E73" s="17" t="s">
         <v>14</v>
       </c>
@@ -2197,7 +2199,7 @@
       <c r="C74" s="21">
         <v>12</v>
       </c>
-      <c r="D74" s="24"/>
+      <c r="D74" s="25"/>
       <c r="E74" s="22" t="s">
         <v>14</v>
       </c>
@@ -2235,7 +2237,7 @@
       <c r="C77" s="15">
         <v>6</v>
       </c>
-      <c r="D77" s="25"/>
+      <c r="D77" s="24"/>
       <c r="E77" s="17" t="s">
         <v>14</v>
       </c>
@@ -2251,7 +2253,7 @@
       <c r="C78" s="21">
         <v>14</v>
       </c>
-      <c r="D78" s="24"/>
+      <c r="D78" s="25"/>
       <c r="E78" s="22" t="s">
         <v>14</v>
       </c>
@@ -2267,7 +2269,7 @@
       <c r="C79" s="15">
         <v>7</v>
       </c>
-      <c r="D79" s="25"/>
+      <c r="D79" s="24"/>
       <c r="E79" s="17" t="s">
         <v>14</v>
       </c>
@@ -2283,7 +2285,7 @@
       <c r="C80" s="21">
         <v>12</v>
       </c>
-      <c r="D80" s="24"/>
+      <c r="D80" s="25"/>
       <c r="E80" s="22" t="s">
         <v>14</v>
       </c>
@@ -2299,7 +2301,7 @@
       <c r="C81" s="15">
         <v>8</v>
       </c>
-      <c r="D81" s="25"/>
+      <c r="D81" s="24"/>
       <c r="E81" s="17" t="s">
         <v>14</v>
       </c>
@@ -2315,7 +2317,7 @@
       <c r="C82" s="21">
         <v>6</v>
       </c>
-      <c r="D82" s="24"/>
+      <c r="D82" s="25"/>
       <c r="E82" s="22" t="s">
         <v>14</v>
       </c>
@@ -2353,7 +2355,7 @@
       <c r="C85" s="15">
         <v>1</v>
       </c>
-      <c r="D85" s="25"/>
+      <c r="D85" s="24"/>
       <c r="E85" s="17" t="s">
         <v>14</v>
       </c>
@@ -2369,7 +2371,7 @@
       <c r="C86" s="21">
         <v>5</v>
       </c>
-      <c r="D86" s="24"/>
+      <c r="D86" s="25"/>
       <c r="E86" s="22" t="s">
         <v>14</v>
       </c>
@@ -2385,7 +2387,7 @@
       <c r="C87" s="15">
         <v>7</v>
       </c>
-      <c r="D87" s="25"/>
+      <c r="D87" s="24"/>
       <c r="E87" s="17" t="s">
         <v>14</v>
       </c>
@@ -2401,7 +2403,7 @@
       <c r="C88" s="21">
         <v>9</v>
       </c>
-      <c r="D88" s="24"/>
+      <c r="D88" s="25"/>
       <c r="E88" s="22" t="s">
         <v>14</v>
       </c>
@@ -2417,7 +2419,7 @@
       <c r="C89" s="15">
         <v>10</v>
       </c>
-      <c r="D89" s="25"/>
+      <c r="D89" s="24"/>
       <c r="E89" s="17" t="s">
         <v>14</v>
       </c>
@@ -2433,7 +2435,7 @@
       <c r="C90" s="21">
         <v>6</v>
       </c>
-      <c r="D90" s="24"/>
+      <c r="D90" s="25"/>
       <c r="E90" s="22" t="s">
         <v>14</v>
       </c>
@@ -2449,7 +2451,7 @@
       <c r="C91" s="15">
         <v>5</v>
       </c>
-      <c r="D91" s="25"/>
+      <c r="D91" s="24"/>
       <c r="E91" s="17" t="s">
         <v>14</v>
       </c>
@@ -2465,7 +2467,7 @@
       <c r="C92" s="21">
         <v>7</v>
       </c>
-      <c r="D92" s="24"/>
+      <c r="D92" s="25"/>
       <c r="E92" s="22" t="s">
         <v>14</v>
       </c>
@@ -2481,7 +2483,7 @@
       <c r="C93" s="15">
         <v>1</v>
       </c>
-      <c r="D93" s="25"/>
+      <c r="D93" s="24"/>
       <c r="E93" s="17" t="s">
         <v>14</v>
       </c>
@@ -2497,7 +2499,7 @@
       <c r="C94" s="21">
         <v>5</v>
       </c>
-      <c r="D94" s="24"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="22" t="s">
         <v>14</v>
       </c>
@@ -2535,7 +2537,7 @@
       <c r="C97" s="15">
         <v>1</v>
       </c>
-      <c r="D97" s="25"/>
+      <c r="D97" s="24"/>
       <c r="E97" s="17" t="s">
         <v>14</v>
       </c>
@@ -2551,7 +2553,7 @@
       <c r="C98" s="21">
         <v>6</v>
       </c>
-      <c r="D98" s="24"/>
+      <c r="D98" s="25"/>
       <c r="E98" s="22" t="s">
         <v>14</v>
       </c>
@@ -2589,7 +2591,7 @@
       <c r="C101" s="15">
         <v>9</v>
       </c>
-      <c r="D101" s="25"/>
+      <c r="D101" s="24"/>
       <c r="E101" s="17" t="s">
         <v>14</v>
       </c>
